--- a/Cardamyst Affordability Model.xlsx
+++ b/Cardamyst Affordability Model.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,15 +20,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="+0.00%;-0.00%"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;+#,##0;[Red]&quot;$&quot;-#,##0"/>
+    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="169" formatCode="+0.00%;-0.00%"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;+#,##0;[Red]&quot;$&quot;-#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,12 +75,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0054575E"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
@@ -119,15 +113,19 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="0054575E"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="00E31D93"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E31D93"/>
-      <sz val="14"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -139,24 +137,6 @@
       <name val="Calibri"/>
       <color rgb="0071B4BE"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00E31D93"/>
-      <sz val="28"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00172852"/>
-      <sz val="22"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0071B4BE"/>
-      <sz val="22"/>
     </font>
   </fonts>
   <fills count="9">
@@ -249,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -261,11 +241,10 @@
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -277,33 +256,34 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -407,11 +387,11 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Charts'!B7</f>
+              <f>'Charts'!B6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="30000">
               <a:solidFill>
                 <a:srgbClr val="E31D93"/>
               </a:solidFill>
@@ -419,12 +399,8 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E31D93"/>
-              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -432,12 +408,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$8:$A$19</f>
+              <f>'Charts'!$A$7:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$8:$B$19</f>
+              <f>'Charts'!$B$7:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -449,24 +425,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Month</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -476,7 +439,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -534,11 +496,11 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Charts'!B7</f>
+              <f>'Charts'!B6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="30000">
               <a:solidFill>
                 <a:srgbClr val="E31D93"/>
               </a:solidFill>
@@ -555,12 +517,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Charts'!$A$8:$A$19</f>
+              <f>'Charts'!$A$7:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$B$8:$B$19</f>
+              <f>'Charts'!$B$7:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -574,11 +536,11 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Charts'!C7</f>
+              <f>'Charts'!C6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="30000">
               <a:solidFill>
                 <a:srgbClr val="71B4BE"/>
               </a:solidFill>
@@ -595,7 +557,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Charts'!$C$8:$C$19</f>
+              <f>'Charts'!$C$7:$C$18</f>
             </numRef>
           </val>
         </ser>
@@ -607,9 +569,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -619,7 +583,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -647,7 +610,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -705,7 +667,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Charts'!D7</f>
+              <f>'Charts'!D6</f>
             </strRef>
           </tx>
           <spPr>
@@ -718,12 +680,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$8:$A$19</f>
+              <f>'Charts'!$A$7:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$D$8:$D$19</f>
+              <f>'Charts'!$D$7:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -732,7 +694,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Charts'!E7</f>
+              <f>'Charts'!E6</f>
             </strRef>
           </tx>
           <spPr>
@@ -745,12 +707,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts'!$A$8:$A$19</f>
+              <f>'Charts'!$A$7:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts'!$E$8:$E$19</f>
+              <f>'Charts'!$E$7:$E$18</f>
             </numRef>
           </val>
         </ser>
@@ -763,9 +725,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -775,7 +739,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -819,96 +782,98 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Scenario GTN % Comparison</a:t>
+              <a:t>Baseline vs Scenario GTN %</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios'!B20</f>
+              <f>'Scenarios'!B25</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+              <a:solidFill>
+                <a:srgbClr val="172852"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <dPt>
-            <idx val="0"/>
+          <marker>
+            <symbol val="none"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="172852"/>
-              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Scenarios'!$A$26:$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios'!$B$26:$B$37</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25000">
+              <a:solidFill>
                 <a:srgbClr val="E31D93"/>
               </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="71B4BE"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="00B2E3"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
+          </marker>
           <cat>
             <numRef>
-              <f>'Scenarios'!$A$21:$A$24</f>
+              <f>'Scenarios'!$A$26:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$B$21:$B$24</f>
+              <f>'Scenarios'!$C$26:$C$37</f>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
-      </barChart>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -918,7 +883,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1018,7 +982,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3600000"/>
+    <ext cx="5760000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1037,10 +1001,10 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3600000"/>
+    <ext cx="5760000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1059,10 +1023,10 @@
     <from>
       <col>7</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3600000"/>
+    <ext cx="5760000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1109,12 +1073,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="4320000"/>
+    <ext cx="5760000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1158,36 +1122,6 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="476250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1666,304 +1600,304 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Higher coverage = Lower GTN (less not-covered buydown)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <f>REPT("█",ROUND(C22*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <f>REPT("█",ROUND(C23*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <f>REPT("█",ROUND(C24*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <f>REPT("█",ROUND(C25*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="11" t="n">
         <v>0.11</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <f>REPT("█",ROUND(C26*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="11" t="n">
         <v>0.29</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <f>REPT("█",ROUND(C27*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.44</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <f>REPT("█",ROUND(C28*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="11" t="n">
         <v>0.52</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <f>REPT("█",ROUND(C29*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <f>REPT("█",ROUND(C30*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="C31" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <f>REPT("█",ROUND(C31*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="12">
         <f>REPT("█",ROUND(C32*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <f>REPT("█",ROUND(C33*20,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>DEDUCTIBLE MET (% by Month)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="11" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="C37" s="11" t="n">
         <v>0.11</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="11" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="11" t="n">
         <v>0.295</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="11" t="n">
         <v>0.395</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="11" t="n">
         <v>0.495</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
+      <c r="C42" s="11" t="n">
         <v>0.595</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="11" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C44" s="11" t="n">
         <v>0.785</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="11" t="n">
         <v>0.885</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="11" t="n">
         <v>0.949</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
+      <c r="C47" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -1975,122 +1909,122 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
+      <c r="C50" s="11" t="n">
         <v>0.96</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
+      <c r="C51" s="11" t="n">
         <v>0.96</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
+      <c r="C52" s="11" t="n">
         <v>0.96</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
+      <c r="C53" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
+      <c r="C54" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
+      <c r="C55" s="11" t="n">
         <v>0.95</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="C56" s="12" t="n">
+      <c r="C56" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="C57" s="12" t="n">
+      <c r="C57" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="C58" s="12" t="n">
+      <c r="C58" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="C59" s="12" t="n">
+      <c r="C59" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="C60" s="12" t="n">
+      <c r="C60" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="C61" s="12" t="n">
+      <c r="C61" s="11" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -2137,79 +2071,79 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>DETAILED AFFORDABILITY MODEL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="15" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="17" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Jan</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Feb</t>
         </is>
       </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Mar</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Apr</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Jun</t>
         </is>
       </c>
-      <c r="K3" s="17" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>Jul</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
         <is>
           <t>Aug</t>
         </is>
       </c>
-      <c r="M3" s="17" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>Sep</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t>Oct</t>
         </is>
       </c>
-      <c r="O3" s="17" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t>Nov</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
         <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="Q3" s="16" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>ANNUAL</t>
         </is>
@@ -2226,50 +2160,45 @@
           <t>TRx Forecast (Covered Commercial)</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="17" t="n">
         <v>50.23</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="17" t="n">
         <v>83.78</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="17" t="n">
         <v>131.82</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="I4" s="17" t="n">
         <v>300.71</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="17" t="n">
         <v>667.02</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="K4" s="17" t="n">
         <v>1151.06</v>
       </c>
-      <c r="L4" s="18" t="n">
+      <c r="L4" s="17" t="n">
         <v>1505.31</v>
       </c>
-      <c r="M4" s="18" t="n">
+      <c r="M4" s="17" t="n">
         <v>1940.22</v>
       </c>
-      <c r="N4" s="18" t="n">
+      <c r="N4" s="17" t="n">
         <v>2448.98</v>
       </c>
-      <c r="O4" s="18" t="n">
+      <c r="O4" s="17" t="n">
         <v>2812.1</v>
       </c>
-      <c r="P4" s="18" t="n">
+      <c r="P4" s="17" t="n">
         <v>3322.67</v>
       </c>
-      <c r="Q4" s="19">
+      <c r="Q4" s="18">
         <f>SUM(E4:P4)</f>
         <v/>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>From Demand Forecast</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -2278,106 +2207,106 @@
           <t>TRx Forecast (Not Covered Commercial)</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="17" t="n">
         <v>64.58</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="17" t="n">
         <v>104</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="17" t="n">
         <v>158.18</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="17" t="n">
         <v>199.99</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="17" t="n">
         <v>192.77</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="K5" s="17" t="n">
         <v>194.47</v>
       </c>
-      <c r="L5" s="18" t="n">
+      <c r="L5" s="17" t="n">
         <v>249.11</v>
       </c>
-      <c r="M5" s="18" t="n">
+      <c r="M5" s="17" t="n">
         <v>350.07</v>
       </c>
-      <c r="N5" s="18" t="n">
+      <c r="N5" s="17" t="n">
         <v>191</v>
       </c>
-      <c r="O5" s="18" t="n">
+      <c r="O5" s="17" t="n">
         <v>281.41</v>
       </c>
-      <c r="P5" s="18" t="n">
+      <c r="P5" s="17" t="n">
         <v>359.88</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="Q5" s="18">
         <f>SUM(E5:P5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Coverage Uptake %</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="20">
         <f>Assumptions!C22</f>
         <v/>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <f>Assumptions!C23</f>
         <v/>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="20">
         <f>Assumptions!C24</f>
         <v/>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="20">
         <f>Assumptions!C25</f>
         <v/>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <f>Assumptions!C26</f>
         <v/>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="20">
         <f>Assumptions!C27</f>
         <v/>
       </c>
-      <c r="K6" s="21">
+      <c r="K6" s="20">
         <f>Assumptions!C28</f>
         <v/>
       </c>
-      <c r="L6" s="21">
+      <c r="L6" s="20">
         <f>Assumptions!C29</f>
         <v/>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="20">
         <f>Assumptions!C30</f>
         <v/>
       </c>
-      <c r="N6" s="21">
+      <c r="N6" s="20">
         <f>Assumptions!C31</f>
         <v/>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="20">
         <f>Assumptions!C32</f>
         <v/>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="20">
         <f>Assumptions!C33</f>
         <v/>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="21">
         <f>AVERAGE(E6:P6)</f>
         <v/>
       </c>
-      <c r="R6" s="23" t="inlineStr">
+      <c r="R6" s="22" t="inlineStr">
         <is>
           <t>KEY: From Coverage Tracker</t>
         </is>
@@ -2389,51 +2318,51 @@
           <t>Payer Mix (Commercial)</t>
         </is>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <f>Assumptions!C50</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="23">
         <f>Assumptions!C51</f>
         <v/>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <f>Assumptions!C52</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <f>Assumptions!C53</f>
         <v/>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="23">
         <f>Assumptions!C54</f>
         <v/>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="23">
         <f>Assumptions!C55</f>
         <v/>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="23">
         <f>Assumptions!C56</f>
         <v/>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="23">
         <f>Assumptions!C57</f>
         <v/>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="23">
         <f>Assumptions!C58</f>
         <v/>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="23">
         <f>Assumptions!C59</f>
         <v/>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="23">
         <f>Assumptions!C60</f>
         <v/>
       </c>
-      <c r="P7" s="24">
+      <c r="P7" s="23">
         <f>Assumptions!C61</f>
         <v/>
       </c>
@@ -2444,62 +2373,57 @@
           <t>% Covered Claims</t>
         </is>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <f>E6+((1-E6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <f>F6+((1-F6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <f>G6+((1-G6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <f>H6+((1-H6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="21">
         <f>I6+((1-I6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="21">
         <f>J6+((1-J6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="21">
         <f>K6+((1-K6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="21">
         <f>L6+((1-L6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="21">
         <f>M6+((1-M6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="N8" s="22">
+      <c r="N8" s="21">
         <f>N6+((1-N6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="O8" s="22">
+      <c r="O8" s="21">
         <f>O6+((1-O6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="P8" s="22">
+      <c r="P8" s="21">
         <f>P6+((1-P6)*Assumptions!$C$11)</f>
         <v/>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8" s="21">
         <f>AVERAGE(E8:P8)</f>
         <v/>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Coverage + Exception Pullthrough</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -2508,55 +2432,55 @@
           <t>% Not Covered Claims</t>
         </is>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <f>1-E8</f>
         <v/>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <f>1-F8</f>
         <v/>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <f>1-G8</f>
         <v/>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <f>1-H8</f>
         <v/>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="21">
         <f>1-I8</f>
         <v/>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="21">
         <f>1-J8</f>
         <v/>
       </c>
-      <c r="K9" s="22">
+      <c r="K9" s="21">
         <f>1-K8</f>
         <v/>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="21">
         <f>1-L8</f>
         <v/>
       </c>
-      <c r="M9" s="22">
+      <c r="M9" s="21">
         <f>1-M8</f>
         <v/>
       </c>
-      <c r="N9" s="22">
+      <c r="N9" s="21">
         <f>1-N8</f>
         <v/>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="21">
         <f>1-O8</f>
         <v/>
       </c>
-      <c r="P9" s="22">
+      <c r="P9" s="21">
         <f>1-P8</f>
         <v/>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9" s="21">
         <f>AVERAGE(E9:P9)</f>
         <v/>
       </c>
@@ -2567,51 +2491,51 @@
           <t>% Met Deductible</t>
         </is>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="21">
         <f>Assumptions!C36</f>
         <v/>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <f>Assumptions!C37</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <f>Assumptions!C38</f>
         <v/>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <f>Assumptions!C39</f>
         <v/>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="21">
         <f>Assumptions!C40</f>
         <v/>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="21">
         <f>Assumptions!C41</f>
         <v/>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="21">
         <f>Assumptions!C42</f>
         <v/>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="21">
         <f>Assumptions!C43</f>
         <v/>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="21">
         <f>Assumptions!C44</f>
         <v/>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="21">
         <f>Assumptions!C45</f>
         <v/>
       </c>
-      <c r="O10" s="22">
+      <c r="O10" s="21">
         <f>Assumptions!C46</f>
         <v/>
       </c>
-      <c r="P10" s="22">
+      <c r="P10" s="21">
         <f>Assumptions!C47</f>
         <v/>
       </c>
@@ -2622,51 +2546,51 @@
           <t>% Copay Structure</t>
         </is>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="K11" s="22">
+      <c r="K11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="L11" s="22">
+      <c r="L11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="N11" s="22">
+      <c r="N11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="O11" s="22">
+      <c r="O11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="P11" s="22">
+      <c r="P11" s="21">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
@@ -2677,51 +2601,51 @@
           <t>Copay Amount</t>
         </is>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="P12" s="25">
+      <c r="P12" s="24">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
@@ -2732,51 +2656,51 @@
           <t>Copay Buydown</t>
         </is>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="24">
         <f>E12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f>F12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <f>G12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <f>H12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <f>I12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <f>J12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="24">
         <f>K12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="24">
         <f>L12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="24">
         <f>M12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="24">
         <f>N12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="O13" s="25">
+      <c r="O13" s="24">
         <f>O12-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="P13" s="25">
+      <c r="P13" s="24">
         <f>P12-Assumptions!$C$9</f>
         <v/>
       </c>
@@ -2787,51 +2711,51 @@
           <t>% Coinsurance Structure</t>
         </is>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="M14" s="22">
+      <c r="M14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="N14" s="22">
+      <c r="N14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="O14" s="22">
+      <c r="O14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="P14" s="22">
+      <c r="P14" s="21">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
@@ -2842,51 +2766,51 @@
           <t>Coinsurance Amount</t>
         </is>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="L15" s="25">
+      <c r="L15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="N15" s="25">
+      <c r="N15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="P15" s="25">
+      <c r="P15" s="24">
         <f>Assumptions!$C$17*Assumptions!$C$8</f>
         <v/>
       </c>
@@ -2897,51 +2821,51 @@
           <t>Coinsurance Buydown</t>
         </is>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <f>E15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <f>F15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <f>G15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <f>H15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <f>I15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <f>J15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="24">
         <f>K15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="24">
         <f>L15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="24">
         <f>M15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="24">
         <f>N15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="O16" s="25">
+      <c r="O16" s="24">
         <f>O15-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="P16" s="25">
+      <c r="P16" s="24">
         <f>P15-Assumptions!$C$9</f>
         <v/>
       </c>
@@ -2952,51 +2876,51 @@
           <t>Not Met Deductible Buydown</t>
         </is>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="L17" s="25">
+      <c r="L17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="M17" s="25">
+      <c r="M17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="P17" s="25">
+      <c r="P17" s="24">
         <f>Assumptions!$C$8-Assumptions!$C$9</f>
         <v/>
       </c>
@@ -3007,55 +2931,55 @@
           <t>Avg Covered Discount %</t>
         </is>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="25">
         <f>((E11*E13/Assumptions!$C$8)+(E14*E16/Assumptions!$C$8))*E10+((1-E10)*E17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="25">
         <f>((F11*F13/Assumptions!$C$8)+(F14*F16/Assumptions!$C$8))*F10+((1-F10)*F17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="25">
         <f>((G11*G13/Assumptions!$C$8)+(G14*G16/Assumptions!$C$8))*G10+((1-G10)*G17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="25">
         <f>((H11*H13/Assumptions!$C$8)+(H14*H16/Assumptions!$C$8))*H10+((1-H10)*H17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="25">
         <f>((I11*I13/Assumptions!$C$8)+(I14*I16/Assumptions!$C$8))*I10+((1-I10)*I17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="25">
         <f>((J11*J13/Assumptions!$C$8)+(J14*J16/Assumptions!$C$8))*J10+((1-J10)*J17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="K18" s="26">
+      <c r="K18" s="25">
         <f>((K11*K13/Assumptions!$C$8)+(K14*K16/Assumptions!$C$8))*K10+((1-K10)*K17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="L18" s="26">
+      <c r="L18" s="25">
         <f>((L11*L13/Assumptions!$C$8)+(L14*L16/Assumptions!$C$8))*L10+((1-L10)*L17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="M18" s="26">
+      <c r="M18" s="25">
         <f>((M11*M13/Assumptions!$C$8)+(M14*M16/Assumptions!$C$8))*M10+((1-M10)*M17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="N18" s="26">
+      <c r="N18" s="25">
         <f>((N11*N13/Assumptions!$C$8)+(N14*N16/Assumptions!$C$8))*N10+((1-N10)*N17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="O18" s="26">
+      <c r="O18" s="25">
         <f>((O11*O13/Assumptions!$C$8)+(O14*O16/Assumptions!$C$8))*O10+((1-O10)*O17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="P18" s="26">
+      <c r="P18" s="25">
         <f>((P11*P13/Assumptions!$C$8)+(P14*P16/Assumptions!$C$8))*P10+((1-P10)*P17/Assumptions!$C$8)</f>
         <v/>
       </c>
-      <c r="Q18" s="26">
+      <c r="Q18" s="25">
         <f>AVERAGE(E18:P18)</f>
         <v/>
       </c>
@@ -3066,55 +2990,55 @@
           <t>Avg Covered Benefit ($)</t>
         </is>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="24">
         <f>E18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <f>F18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <f>G18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="24">
         <f>H18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <f>I18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="24">
         <f>J18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="24">
         <f>K18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="L19" s="25">
+      <c r="L19" s="24">
         <f>L18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="M19" s="25">
+      <c r="M19" s="24">
         <f>M18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="N19" s="25">
+      <c r="N19" s="24">
         <f>N18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="O19" s="25">
+      <c r="O19" s="24">
         <f>O18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="P19" s="25">
+      <c r="P19" s="24">
         <f>P18*Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="Q19" s="25">
+      <c r="Q19" s="24">
         <f>AVERAGE(E19:P19)</f>
         <v/>
       </c>
@@ -3125,58 +3049,53 @@
           <t>Not Covered Benefit ($)</t>
         </is>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="L20" s="25">
+      <c r="L20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="M20" s="25">
+      <c r="M20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="N20" s="25">
+      <c r="N20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="O20" s="25">
+      <c r="O20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="P20" s="25">
+      <c r="P20" s="24">
         <f>Assumptions!$C$18</f>
         <v/>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>Buydown to $35</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -3185,51 +3104,51 @@
           <t>Redemption Rate</t>
         </is>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="K21" s="22">
+      <c r="K21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="N21" s="22">
+      <c r="N21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="O21" s="22">
+      <c r="O21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="P21" s="22">
+      <c r="P21" s="21">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
@@ -3240,174 +3159,169 @@
           <t>WAC Price</t>
         </is>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="M22" s="25">
+      <c r="M22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
-      <c r="P22" s="25">
+      <c r="P22" s="24">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>Covered Program Costs</t>
         </is>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <f>E4*E21*E19</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="27">
         <f>F4*F21*F19</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="27">
         <f>G4*G21*G19</f>
         <v/>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="27">
         <f>H4*H21*H19</f>
         <v/>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="27">
         <f>I4*I21*I19</f>
         <v/>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="27">
         <f>J4*J21*J19</f>
         <v/>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="27">
         <f>K4*K21*K19</f>
         <v/>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="27">
         <f>L4*L21*L19</f>
         <v/>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="27">
         <f>M4*M21*M19</f>
         <v/>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="27">
         <f>N4*N21*N19</f>
         <v/>
       </c>
-      <c r="O23" s="28">
+      <c r="O23" s="27">
         <f>O4*O21*O19</f>
         <v/>
       </c>
-      <c r="P23" s="28">
+      <c r="P23" s="27">
         <f>P4*P21*P19</f>
         <v/>
       </c>
-      <c r="Q23" s="28">
+      <c r="Q23" s="27">
         <f>SUM(E23:P23)</f>
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>TRx × Redemption × Benefit</t>
-        </is>
-      </c>
     </row>
     <row r="24">
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Not Covered Program Costs</t>
         </is>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <f>E5*E7*E21*E20</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="27">
         <f>F5*F7*F21*F20</f>
         <v/>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="27">
         <f>G5*G7*G21*G20</f>
         <v/>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="27">
         <f>H5*H7*H21*H20</f>
         <v/>
       </c>
-      <c r="I24" s="28">
+      <c r="I24" s="27">
         <f>I5*I7*I21*I20</f>
         <v/>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="27">
         <f>J5*J7*J21*J20</f>
         <v/>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="27">
         <f>K5*K7*K21*K20</f>
         <v/>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="27">
         <f>L5*L7*L21*L20</f>
         <v/>
       </c>
-      <c r="M24" s="28">
+      <c r="M24" s="27">
         <f>M5*M7*M21*M20</f>
         <v/>
       </c>
-      <c r="N24" s="28">
+      <c r="N24" s="27">
         <f>N5*N7*N21*N20</f>
         <v/>
       </c>
-      <c r="O24" s="28">
+      <c r="O24" s="27">
         <f>O5*O7*O21*O20</f>
         <v/>
       </c>
-      <c r="P24" s="28">
+      <c r="P24" s="27">
         <f>P5*P7*P21*P20</f>
         <v/>
       </c>
-      <c r="Q24" s="28">
+      <c r="Q24" s="27">
         <f>SUM(E24:P24)</f>
         <v/>
       </c>
@@ -3418,55 +3332,55 @@
           <t>TOTAL PROGRAM COSTS</t>
         </is>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="28">
         <f>E23+E24</f>
         <v/>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="28">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="28">
         <f>G23+G24</f>
         <v/>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="28">
         <f>H23+H24</f>
         <v/>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="28">
         <f>I23+I24</f>
         <v/>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="28">
         <f>J23+J24</f>
         <v/>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="28">
         <f>K23+K24</f>
         <v/>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="28">
         <f>L23+L24</f>
         <v/>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="28">
         <f>M23+M24</f>
         <v/>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="28">
         <f>N23+N24</f>
         <v/>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="28">
         <f>O23+O24</f>
         <v/>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="28">
         <f>P23+P24</f>
         <v/>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="28">
         <f>SUM(E25:P25)</f>
         <v/>
       </c>
@@ -3477,55 +3391,55 @@
           <t>Gross Demand Sales</t>
         </is>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="24">
         <f>(E4+E5)*E22</f>
         <v/>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="24">
         <f>(F4+F5)*F22</f>
         <v/>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <f>(G4+G5)*G22</f>
         <v/>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="24">
         <f>(H4+H5)*H22</f>
         <v/>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="24">
         <f>(I4+I5)*I22</f>
         <v/>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="24">
         <f>(J4+J5)*J22</f>
         <v/>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="24">
         <f>(K4+K5)*K22</f>
         <v/>
       </c>
-      <c r="L26" s="25">
+      <c r="L26" s="24">
         <f>(L4+L5)*L22</f>
         <v/>
       </c>
-      <c r="M26" s="25">
+      <c r="M26" s="24">
         <f>(M4+M5)*M22</f>
         <v/>
       </c>
-      <c r="N26" s="25">
+      <c r="N26" s="24">
         <f>(N4+N5)*N22</f>
         <v/>
       </c>
-      <c r="O26" s="25">
+      <c r="O26" s="24">
         <f>(O4+O5)*O22</f>
         <v/>
       </c>
-      <c r="P26" s="25">
+      <c r="P26" s="24">
         <f>(P4+P5)*P22</f>
         <v/>
       </c>
-      <c r="Q26" s="25">
+      <c r="Q26" s="24">
         <f>SUM(E26:P26)</f>
         <v/>
       </c>
@@ -3536,59 +3450,59 @@
           <t>GTN % (Copay/Denial)</t>
         </is>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <f>IFERROR(E25/E26,0)</f>
         <v/>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="29">
         <f>IFERROR(F25/F26,0)</f>
         <v/>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="29">
         <f>IFERROR(G25/G26,0)</f>
         <v/>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="29">
         <f>IFERROR(H25/H26,0)</f>
         <v/>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="29">
         <f>IFERROR(I25/I26,0)</f>
         <v/>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="29">
         <f>IFERROR(J25/J26,0)</f>
         <v/>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="29">
         <f>IFERROR(K25/K26,0)</f>
         <v/>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="29">
         <f>IFERROR(L25/L26,0)</f>
         <v/>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="29">
         <f>IFERROR(M25/M26,0)</f>
         <v/>
       </c>
-      <c r="N27" s="30">
+      <c r="N27" s="29">
         <f>IFERROR(N25/N26,0)</f>
         <v/>
       </c>
-      <c r="O27" s="30">
+      <c r="O27" s="29">
         <f>IFERROR(O25/O26,0)</f>
         <v/>
       </c>
-      <c r="P27" s="30">
+      <c r="P27" s="29">
         <f>IFERROR(P25/P26,0)</f>
         <v/>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="29">
         <f>IFERROR(Q25/Q26,0)</f>
         <v/>
       </c>
-      <c r="R27" s="31" t="inlineStr">
+      <c r="R27" s="30" t="inlineStr">
         <is>
           <t>KEY OUTPUT</t>
         </is>
@@ -3600,55 +3514,55 @@
           <t>Net Sales (After GTN)</t>
         </is>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="24">
         <f>E26-E25</f>
         <v/>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="24">
         <f>F26-F25</f>
         <v/>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="24">
         <f>G26-G25</f>
         <v/>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="24">
         <f>H26-H25</f>
         <v/>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="24">
         <f>I26-I25</f>
         <v/>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="24">
         <f>J26-J25</f>
         <v/>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="24">
         <f>K26-K25</f>
         <v/>
       </c>
-      <c r="L28" s="25">
+      <c r="L28" s="24">
         <f>L26-L25</f>
         <v/>
       </c>
-      <c r="M28" s="25">
+      <c r="M28" s="24">
         <f>M26-M25</f>
         <v/>
       </c>
-      <c r="N28" s="25">
+      <c r="N28" s="24">
         <f>N26-N25</f>
         <v/>
       </c>
-      <c r="O28" s="25">
+      <c r="O28" s="24">
         <f>O26-O25</f>
         <v/>
       </c>
-      <c r="P28" s="25">
+      <c r="P28" s="24">
         <f>P26-P25</f>
         <v/>
       </c>
-      <c r="Q28" s="25">
+      <c r="Q28" s="24">
         <f>SUM(E28:P28)</f>
         <v/>
       </c>
@@ -3668,7 +3582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H31"/>
+  <dimension ref="A4:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3687,475 +3601,427 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Chart Data (Hidden in production)</t>
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>GTN %</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Coverage %</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Covered Cost</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>Not Covered Cost</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>GTN %</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Coverage %</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Covered Cost</t>
-        </is>
-      </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>Not Covered Cost</t>
-        </is>
-      </c>
-      <c r="F7" s="32" t="inlineStr">
-        <is>
-          <t>Total Cost</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B7" s="25">
+        <f>Model!E27</f>
+        <v/>
+      </c>
+      <c r="C7" s="21">
+        <f>Model!E6</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>Model!E23</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>Model!E24</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
+        <f>Model!E25</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="B8" s="26">
-        <f>Model!E27</f>
-        <v/>
-      </c>
-      <c r="C8" s="22">
-        <f>Model!E6</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>Model!E23</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>Model!E24</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>Model!E25</f>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B8" s="25">
+        <f>Model!F27</f>
+        <v/>
+      </c>
+      <c r="C8" s="21">
+        <f>Model!F6</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>Model!F23</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>Model!F24</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>Model!F25</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="B9" s="26">
-        <f>Model!F27</f>
-        <v/>
-      </c>
-      <c r="C9" s="22">
-        <f>Model!F6</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>Model!F23</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>Model!F24</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>Model!F25</f>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B9" s="25">
+        <f>Model!G27</f>
+        <v/>
+      </c>
+      <c r="C9" s="21">
+        <f>Model!G6</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>Model!G23</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>Model!G24</f>
+        <v/>
+      </c>
+      <c r="F9" s="24">
+        <f>Model!G25</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="B10" s="26">
-        <f>Model!G27</f>
-        <v/>
-      </c>
-      <c r="C10" s="22">
-        <f>Model!G6</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>Model!G23</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>Model!G24</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>Model!G25</f>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B10" s="25">
+        <f>Model!H27</f>
+        <v/>
+      </c>
+      <c r="C10" s="21">
+        <f>Model!H6</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>Model!H23</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>Model!H24</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>Model!H25</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="B11" s="26">
-        <f>Model!H27</f>
-        <v/>
-      </c>
-      <c r="C11" s="22">
-        <f>Model!H6</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>Model!H23</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>Model!H24</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>Model!H25</f>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B11" s="25">
+        <f>Model!I27</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>Model!I6</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>Model!I23</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>Model!I24</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>Model!I25</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B12" s="26">
-        <f>Model!I27</f>
-        <v/>
-      </c>
-      <c r="C12" s="22">
-        <f>Model!I6</f>
-        <v/>
-      </c>
-      <c r="D12" s="25">
-        <f>Model!I23</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>Model!I24</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>Model!I25</f>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B12" s="25">
+        <f>Model!J27</f>
+        <v/>
+      </c>
+      <c r="C12" s="21">
+        <f>Model!J6</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>Model!J23</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>Model!J24</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>Model!J25</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="B13" s="26">
-        <f>Model!J27</f>
-        <v/>
-      </c>
-      <c r="C13" s="22">
-        <f>Model!J6</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>Model!J23</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>Model!J24</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>Model!J25</f>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B13" s="25">
+        <f>Model!K27</f>
+        <v/>
+      </c>
+      <c r="C13" s="21">
+        <f>Model!K6</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>Model!K23</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>Model!K24</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>Model!K25</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="B14" s="26">
-        <f>Model!K27</f>
-        <v/>
-      </c>
-      <c r="C14" s="22">
-        <f>Model!K6</f>
-        <v/>
-      </c>
-      <c r="D14" s="25">
-        <f>Model!K23</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>Model!K24</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>Model!K25</f>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B14" s="25">
+        <f>Model!L27</f>
+        <v/>
+      </c>
+      <c r="C14" s="21">
+        <f>Model!L6</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>Model!L23</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>Model!L24</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>Model!L25</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="B15" s="26">
-        <f>Model!L27</f>
-        <v/>
-      </c>
-      <c r="C15" s="22">
-        <f>Model!L6</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>Model!L23</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>Model!L24</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>Model!L25</f>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>Model!M27</f>
+        <v/>
+      </c>
+      <c r="C15" s="21">
+        <f>Model!M6</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>Model!M23</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>Model!M24</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>Model!M25</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="B16" s="26">
-        <f>Model!M27</f>
-        <v/>
-      </c>
-      <c r="C16" s="22">
-        <f>Model!M6</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>Model!M23</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>Model!M24</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>Model!M25</f>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B16" s="25">
+        <f>Model!N27</f>
+        <v/>
+      </c>
+      <c r="C16" s="21">
+        <f>Model!N6</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>Model!N23</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>Model!N24</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>Model!N25</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="B17" s="26">
-        <f>Model!N27</f>
-        <v/>
-      </c>
-      <c r="C17" s="22">
-        <f>Model!N6</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>Model!N23</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>Model!N24</f>
-        <v/>
-      </c>
-      <c r="F17" s="25">
-        <f>Model!N25</f>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>Model!O27</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>Model!O6</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>Model!O23</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>Model!O24</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
+        <f>Model!O25</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <f>Model!O27</f>
-        <v/>
-      </c>
-      <c r="C18" s="22">
-        <f>Model!O6</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>Model!O23</f>
-        <v/>
-      </c>
-      <c r="E18" s="25">
-        <f>Model!O24</f>
-        <v/>
-      </c>
-      <c r="F18" s="25">
-        <f>Model!O25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
           <t>Dec</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B18" s="25">
         <f>Model!P27</f>
         <v/>
       </c>
-      <c r="C19" s="22">
+      <c r="C18" s="21">
         <f>Model!P6</f>
         <v/>
       </c>
-      <c r="D19" s="25">
+      <c r="D18" s="24">
         <f>Model!P23</f>
         <v/>
       </c>
-      <c r="E19" s="25">
+      <c r="E18" s="24">
         <f>Model!P24</f>
         <v/>
       </c>
-      <c r="F19" s="25">
+      <c r="F18" s="24">
         <f>Model!P25</f>
         <v/>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>KEY METRICS</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSIGHTS</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Annual GTN %</t>
+        </is>
+      </c>
+      <c r="C22" s="32">
+        <f>Model!Q27</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Annual GTN %:</t>
-        </is>
-      </c>
-      <c r="C23" s="33">
-        <f>Model!Q27</f>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Program Costs</t>
+        </is>
+      </c>
+      <c r="C23" s="24">
+        <f>Model!Q25</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Total Program Costs:</t>
-        </is>
-      </c>
-      <c r="C24" s="34">
-        <f>Model!Q25</f>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Covered Costs</t>
+        </is>
+      </c>
+      <c r="C24" s="24">
+        <f>Model!Q23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Covered Costs:</t>
-        </is>
-      </c>
-      <c r="C25" s="34">
-        <f>Model!Q23</f>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Not Covered Costs</t>
+        </is>
+      </c>
+      <c r="C25" s="24">
+        <f>Model!Q24</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Not Covered Costs:</t>
-        </is>
-      </c>
-      <c r="C26" s="34">
-        <f>Model!Q24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Avg Coverage:</t>
-        </is>
-      </c>
-      <c r="C27" s="35">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Avg Coverage</t>
+        </is>
+      </c>
+      <c r="C26" s="21">
         <f>AVERAGE(Model!E6:P6)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Coverage Impact:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>If coverage +10%:</t>
-        </is>
-      </c>
-      <c r="C30" s="33">
-        <f>Model!Q27*(1-0.08)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>If coverage -10%:</t>
-        </is>
-      </c>
-      <c r="C31" s="33">
-        <f>Model!Q27*(1+0.08)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="2">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4168,393 +4034,1017 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:G33"/>
+  <dimension ref="A4:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SCENARIO COMPARISON</t>
+          <t>SCENARIO ANALYSIS - MONTHLY VIEW</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>Toggle assumptions to see instant GTN impact</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>For Finance Accruals: Edit PURPLE cells to model alternative coverage scenarios by month</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SCENARIO INPUTS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>Current Model</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Low Coverage</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>High Coverage</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>High Exceptions</t>
+          <t>BASELINE (Current Model)</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="O7" s="15" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="Q7" s="15" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Avg Coverage Uptake</t>
-        </is>
-      </c>
-      <c r="C8" s="22">
-        <f>AVERAGE(Assumptions!C22:C33)</f>
-        <v/>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="37" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F8" s="22">
-        <f>C8</f>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Coverage Uptake</t>
+        </is>
+      </c>
+      <c r="E8" s="23">
+        <f>Assumptions!C22</f>
+        <v/>
+      </c>
+      <c r="F8" s="23">
+        <f>Assumptions!C23</f>
+        <v/>
+      </c>
+      <c r="G8" s="23">
+        <f>Assumptions!C24</f>
+        <v/>
+      </c>
+      <c r="H8" s="23">
+        <f>Assumptions!C25</f>
+        <v/>
+      </c>
+      <c r="I8" s="23">
+        <f>Assumptions!C26</f>
+        <v/>
+      </c>
+      <c r="J8" s="23">
+        <f>Assumptions!C27</f>
+        <v/>
+      </c>
+      <c r="K8" s="23">
+        <f>Assumptions!C28</f>
+        <v/>
+      </c>
+      <c r="L8" s="23">
+        <f>Assumptions!C29</f>
+        <v/>
+      </c>
+      <c r="M8" s="23">
+        <f>Assumptions!C30</f>
+        <v/>
+      </c>
+      <c r="N8" s="23">
+        <f>Assumptions!C31</f>
+        <v/>
+      </c>
+      <c r="O8" s="23">
+        <f>Assumptions!C32</f>
+        <v/>
+      </c>
+      <c r="P8" s="23">
+        <f>Assumptions!C33</f>
+        <v/>
+      </c>
+      <c r="Q8" s="21">
+        <f>AVERAGE(E8:P8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Medical Exception Rate</t>
-        </is>
-      </c>
-      <c r="C9" s="22">
-        <f>Assumptions!C11</f>
-        <v/>
-      </c>
-      <c r="D9" s="22">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="F9" s="37" t="n">
-        <v>0.15</v>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>GTN %</t>
+        </is>
+      </c>
+      <c r="E9" s="25">
+        <f>Model!E27</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>Model!F27</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>Model!G27</f>
+        <v/>
+      </c>
+      <c r="H9" s="25">
+        <f>Model!H27</f>
+        <v/>
+      </c>
+      <c r="I9" s="25">
+        <f>Model!I27</f>
+        <v/>
+      </c>
+      <c r="J9" s="25">
+        <f>Model!J27</f>
+        <v/>
+      </c>
+      <c r="K9" s="25">
+        <f>Model!K27</f>
+        <v/>
+      </c>
+      <c r="L9" s="25">
+        <f>Model!L27</f>
+        <v/>
+      </c>
+      <c r="M9" s="25">
+        <f>Model!M27</f>
+        <v/>
+      </c>
+      <c r="N9" s="25">
+        <f>Model!N27</f>
+        <v/>
+      </c>
+      <c r="O9" s="25">
+        <f>Model!O27</f>
+        <v/>
+      </c>
+      <c r="P9" s="25">
+        <f>Model!P27</f>
+        <v/>
+      </c>
+      <c r="Q9" s="25">
+        <f>Model!Q27</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Redemption Rate</t>
-        </is>
-      </c>
-      <c r="C10" s="22">
-        <f>Assumptions!C10</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>C10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Pay No More Than</t>
-        </is>
-      </c>
-      <c r="C11" s="25">
-        <f>Assumptions!C9</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>C11</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>C11</f>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Program Costs</t>
+        </is>
+      </c>
+      <c r="E10" s="24">
+        <f>Model!E25</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>Model!F25</f>
+        <v/>
+      </c>
+      <c r="G10" s="24">
+        <f>Model!G25</f>
+        <v/>
+      </c>
+      <c r="H10" s="24">
+        <f>Model!H25</f>
+        <v/>
+      </c>
+      <c r="I10" s="24">
+        <f>Model!I25</f>
+        <v/>
+      </c>
+      <c r="J10" s="24">
+        <f>Model!J25</f>
+        <v/>
+      </c>
+      <c r="K10" s="24">
+        <f>Model!K25</f>
+        <v/>
+      </c>
+      <c r="L10" s="24">
+        <f>Model!L25</f>
+        <v/>
+      </c>
+      <c r="M10" s="24">
+        <f>Model!M25</f>
+        <v/>
+      </c>
+      <c r="N10" s="24">
+        <f>Model!N25</f>
+        <v/>
+      </c>
+      <c r="O10" s="24">
+        <f>Model!O25</f>
+        <v/>
+      </c>
+      <c r="P10" s="24">
+        <f>Model!P25</f>
+        <v/>
+      </c>
+      <c r="Q10" s="24">
+        <f>SUM(E10:P10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>SCENARIO OUTPUTS</t>
-        </is>
-      </c>
-      <c r="C13" s="38" t="inlineStr">
-        <is>
-          <t>Current Model</t>
-        </is>
-      </c>
-      <c r="D13" s="38" t="inlineStr">
-        <is>
-          <t>Low Coverage</t>
-        </is>
-      </c>
-      <c r="E13" s="38" t="inlineStr">
-        <is>
-          <t>High Coverage</t>
-        </is>
-      </c>
-      <c r="F13" s="38" t="inlineStr">
-        <is>
-          <t>High Exceptions</t>
+          <t>SCENARIO (Edit Coverage Below)</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="H13" s="33" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J13" s="33" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="K13" s="33" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="L13" s="33" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="M13" s="33" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="N13" s="33" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="O13" s="33" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="P13" s="33" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="Q13" s="33" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Estimated Annual GTN %</t>
-        </is>
-      </c>
-      <c r="C14" s="39">
-        <f>Model!Q27</f>
-        <v/>
-      </c>
-      <c r="D14" s="39">
-        <f>C14*(1+(C8-D8)*1.5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="39">
-        <f>C14*(1-(E8-C8)*1.2)</f>
-        <v/>
-      </c>
-      <c r="F14" s="39">
-        <f>C14*(1-F9*0.5)</f>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Scenario Coverage</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I14" s="34" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="J14" s="34" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K14" s="34" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L14" s="34" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M14" s="34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N14" s="34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O14" s="34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P14" s="34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Q14" s="21">
+        <f>AVERAGE(E14:P14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>vs Current Model</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="40">
-        <f>D14-C14</f>
-        <v/>
-      </c>
-      <c r="E15" s="40">
-        <f>E14-C14</f>
-        <v/>
-      </c>
-      <c r="F15" s="40">
-        <f>F14-C14</f>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Scenario GTN %</t>
+        </is>
+      </c>
+      <c r="E15" s="35">
+        <f>MAX(0,E9*(1+(E8-E14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>MAX(0,F9*(1+(F8-F14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="G15" s="35">
+        <f>MAX(0,G9*(1+(G8-G14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="H15" s="35">
+        <f>MAX(0,H9*(1+(H8-H14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="I15" s="35">
+        <f>MAX(0,I9*(1+(I8-I14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>MAX(0,J9*(1+(J8-J14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="K15" s="35">
+        <f>MAX(0,K9*(1+(K8-K14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="L15" s="35">
+        <f>MAX(0,L9*(1+(L8-L14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="M15" s="35">
+        <f>MAX(0,M9*(1+(M8-M14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="N15" s="35">
+        <f>MAX(0,N9*(1+(N8-N14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="O15" s="35">
+        <f>MAX(0,O9*(1+(O8-O14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="P15" s="35">
+        <f>MAX(0,P9*(1+(P8-P14)*1.5))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="25">
+        <f>IFERROR(SUM(E16:P16)/SUM(Model!E26:P26),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Est. Program Cost Impact</t>
-        </is>
-      </c>
-      <c r="C16" s="25">
-        <f>Model!Q25</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>C16*(1+(C8-D8)*1.5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>C16*(1-(E8-C8)*1.2)</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>C16*(1-F9*0.5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>$ Change vs Current</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="41">
-        <f>D16-C16</f>
-        <v/>
-      </c>
-      <c r="E17" s="41">
-        <f>E16-C16</f>
-        <v/>
-      </c>
-      <c r="F17" s="41">
-        <f>F16-C16</f>
-        <v/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Scenario Costs</t>
+        </is>
+      </c>
+      <c r="E16" s="36">
+        <f>E15*Model!E26</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>F15*Model!F26</f>
+        <v/>
+      </c>
+      <c r="G16" s="36">
+        <f>G15*Model!G26</f>
+        <v/>
+      </c>
+      <c r="H16" s="36">
+        <f>H15*Model!H26</f>
+        <v/>
+      </c>
+      <c r="I16" s="36">
+        <f>I15*Model!I26</f>
+        <v/>
+      </c>
+      <c r="J16" s="36">
+        <f>J15*Model!J26</f>
+        <v/>
+      </c>
+      <c r="K16" s="36">
+        <f>K15*Model!K26</f>
+        <v/>
+      </c>
+      <c r="L16" s="36">
+        <f>L15*Model!L26</f>
+        <v/>
+      </c>
+      <c r="M16" s="36">
+        <f>M15*Model!M26</f>
+        <v/>
+      </c>
+      <c r="N16" s="36">
+        <f>N15*Model!N26</f>
+        <v/>
+      </c>
+      <c r="O16" s="36">
+        <f>O15*Model!O26</f>
+        <v/>
+      </c>
+      <c r="P16" s="36">
+        <f>P15*Model!P26</f>
+        <v/>
+      </c>
+      <c r="Q16" s="24">
+        <f>SUM(E16:P16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>DELTA (Scenario - Baseline)</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="H19" s="37" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J19" s="37" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="K19" s="37" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="L19" s="37" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="M19" s="37" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="N19" s="37" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="O19" s="37" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="P19" s="37" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="Q19" s="13" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>GTN %</t>
-        </is>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Δ Coverage</t>
+        </is>
+      </c>
+      <c r="E20" s="38">
+        <f>E14-E8</f>
+        <v/>
+      </c>
+      <c r="F20" s="38">
+        <f>F14-F8</f>
+        <v/>
+      </c>
+      <c r="G20" s="38">
+        <f>G14-G8</f>
+        <v/>
+      </c>
+      <c r="H20" s="38">
+        <f>H14-H8</f>
+        <v/>
+      </c>
+      <c r="I20" s="38">
+        <f>I14-I8</f>
+        <v/>
+      </c>
+      <c r="J20" s="38">
+        <f>J14-J8</f>
+        <v/>
+      </c>
+      <c r="K20" s="38">
+        <f>K14-K8</f>
+        <v/>
+      </c>
+      <c r="L20" s="38">
+        <f>L14-L8</f>
+        <v/>
+      </c>
+      <c r="M20" s="38">
+        <f>M14-M8</f>
+        <v/>
+      </c>
+      <c r="N20" s="38">
+        <f>N14-N8</f>
+        <v/>
+      </c>
+      <c r="O20" s="38">
+        <f>O14-O8</f>
+        <v/>
+      </c>
+      <c r="P20" s="38">
+        <f>P14-P8</f>
+        <v/>
+      </c>
+      <c r="Q20" s="38">
+        <f>AVERAGE(E20:P20)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Current Model</t>
-        </is>
-      </c>
-      <c r="B21" s="26">
-        <f>C14</f>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Δ GTN %</t>
+        </is>
+      </c>
+      <c r="E21" s="39">
+        <f>E15-E9</f>
+        <v/>
+      </c>
+      <c r="F21" s="39">
+        <f>F15-F9</f>
+        <v/>
+      </c>
+      <c r="G21" s="39">
+        <f>G15-G9</f>
+        <v/>
+      </c>
+      <c r="H21" s="39">
+        <f>H15-H9</f>
+        <v/>
+      </c>
+      <c r="I21" s="39">
+        <f>I15-I9</f>
+        <v/>
+      </c>
+      <c r="J21" s="39">
+        <f>J15-J9</f>
+        <v/>
+      </c>
+      <c r="K21" s="39">
+        <f>K15-K9</f>
+        <v/>
+      </c>
+      <c r="L21" s="39">
+        <f>L15-L9</f>
+        <v/>
+      </c>
+      <c r="M21" s="39">
+        <f>M15-M9</f>
+        <v/>
+      </c>
+      <c r="N21" s="39">
+        <f>N15-N9</f>
+        <v/>
+      </c>
+      <c r="O21" s="39">
+        <f>O15-O9</f>
+        <v/>
+      </c>
+      <c r="P21" s="39">
+        <f>P15-P9</f>
+        <v/>
+      </c>
+      <c r="Q21" s="39">
+        <f>Q15-Q9</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Low Coverage</t>
-        </is>
-      </c>
-      <c r="B22" s="26">
-        <f>D14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>High Coverage</t>
-        </is>
-      </c>
-      <c r="B23" s="26">
-        <f>E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>High Exceptions</t>
-        </is>
-      </c>
-      <c r="B24" s="26">
-        <f>F14</f>
-        <v/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Δ Costs ($)</t>
+        </is>
+      </c>
+      <c r="E22" s="40">
+        <f>E16-E10</f>
+        <v/>
+      </c>
+      <c r="F22" s="40">
+        <f>F16-F10</f>
+        <v/>
+      </c>
+      <c r="G22" s="40">
+        <f>G16-G10</f>
+        <v/>
+      </c>
+      <c r="H22" s="40">
+        <f>H16-H10</f>
+        <v/>
+      </c>
+      <c r="I22" s="40">
+        <f>I16-I10</f>
+        <v/>
+      </c>
+      <c r="J22" s="40">
+        <f>J16-J10</f>
+        <v/>
+      </c>
+      <c r="K22" s="40">
+        <f>K16-K10</f>
+        <v/>
+      </c>
+      <c r="L22" s="40">
+        <f>L16-L10</f>
+        <v/>
+      </c>
+      <c r="M22" s="40">
+        <f>M16-M10</f>
+        <v/>
+      </c>
+      <c r="N22" s="40">
+        <f>N16-N10</f>
+        <v/>
+      </c>
+      <c r="O22" s="40">
+        <f>O16-O10</f>
+        <v/>
+      </c>
+      <c r="P22" s="40">
+        <f>P16-P10</f>
+        <v/>
+      </c>
+      <c r="Q22" s="41">
+        <f>Q16-Q10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>Baseline GTN</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>Scenario GTN</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO USE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B26" s="25">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="C26" s="25">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>1. Edit PURPLE cells (row 14) to set scenario coverage by month</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>HOW TO USE SCENARIOS</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B27" s="25">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>2. Watch GTN % and Costs recalculate instantly</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>1. Current Model reflects your actual Assumptions tab settings</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B28" s="25">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>3. DELTA section shows monthly variance for accruals</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>2. Edit the PURPLE cells (D8, E8, F9) to test different scenarios</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B29" s="25">
+        <f>H9</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>H15</f>
+        <v/>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>4. Annual column shows full-year impact</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>3. Watch how GTN % and Program Costs change immediately</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B30" s="25">
+        <f>I9</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>5. Negative Δ Costs = savings from higher coverage</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>4. Low Coverage = More patients go through expensive Not Covered path</t>
-        </is>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B31" s="25">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="C31" s="25">
+        <f>J15</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>5. High Coverage = More patients have formulary access = lower buydown</t>
-        </is>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B32" s="25">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="C32" s="25">
+        <f>K15</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>6. High Exceptions = Medical exceptions approved = treated as covered</t>
-        </is>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B33" s="25">
+        <f>L9</f>
+        <v/>
+      </c>
+      <c r="C33" s="25">
+        <f>L15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B34" s="25">
+        <f>M9</f>
+        <v/>
+      </c>
+      <c r="C34" s="25">
+        <f>M15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B35" s="25">
+        <f>N9</f>
+        <v/>
+      </c>
+      <c r="C35" s="25">
+        <f>N15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B36" s="25">
+        <f>O9</f>
+        <v/>
+      </c>
+      <c r="C36" s="25">
+        <f>O15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B37" s="25">
+        <f>P9</f>
+        <v/>
+      </c>
+      <c r="C37" s="25">
+        <f>P15</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A29:F29"/>
+  <mergeCells count="11">
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="K27:P27"/>
+    <mergeCell ref="K28:P28"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="K26:P26"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="K25:P25"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="K29:P29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4567,7 +5057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:G38"/>
+  <dimension ref="A4:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4584,13 +5074,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>How does GTN change when key assumptions shift?</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -4604,7 +5087,7 @@
           <t>Annual GTN %</t>
         </is>
       </c>
-      <c r="B8" s="42">
+      <c r="B8" s="43">
         <f>Model!Q27</f>
         <v/>
       </c>
@@ -4615,7 +5098,7 @@
           <t>Avg Coverage Uptake</t>
         </is>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <f>AVERAGE(Assumptions!C22:C33)</f>
         <v/>
       </c>
@@ -4626,487 +5109,397 @@
           <t>Medical Exception Rate</t>
         </is>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="21">
         <f>Assumptions!C11</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Redemption Rate</t>
-        </is>
-      </c>
-      <c r="B11" s="22">
-        <f>Assumptions!C10</f>
-        <v/>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>COVERAGE UPTAKE IMPACT</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>COVERAGE UPTAKE IMPACT</t>
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Coverage %</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>Est. GTN %</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>$ Impact</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Visual</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>Coverage %</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="A15" s="44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B15" s="25">
+        <f>$B$8*(1+($B$9-A15)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C15" s="39">
+        <f>B15-$B$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>C15*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E15" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C15*100,0)))&amp;REPT("▲",MAX(0,ROUND(C15*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B16" s="25">
+        <f>$B$8*(1+($B$9-A16)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C16" s="39">
+        <f>B16-$B$8</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>C16*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E16" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C16*100,0)))&amp;REPT("▲",MAX(0,ROUND(C16*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B17" s="25">
+        <f>$B$8*(1+($B$9-A17)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C17" s="39">
+        <f>B17-$B$8</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>C17*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E17" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C17*100,0)))&amp;REPT("▲",MAX(0,ROUND(C17*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B18" s="25">
+        <f>$B$8*(1+($B$9-A18)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C18" s="39">
+        <f>B18-$B$8</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>C18*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E18" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C18*100,0)))&amp;REPT("▲",MAX(0,ROUND(C18*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B19" s="25">
+        <f>$B$8*(1+($B$9-A19)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C19" s="39">
+        <f>B19-$B$8</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>C19*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E19" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C19*100,0)))&amp;REPT("▲",MAX(0,ROUND(C19*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B20" s="25">
+        <f>$B$8*(1+($B$9-A20)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>B20-$B$8</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>C20*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E20" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C20*100,0)))&amp;REPT("▲",MAX(0,ROUND(C20*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B21" s="25">
+        <f>$B$8*(1+($B$9-A21)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C21" s="39">
+        <f>B21-$B$8</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>C21*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E21" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C21*100,0)))&amp;REPT("▲",MAX(0,ROUND(C21*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B22" s="25">
+        <f>$B$8*(1+($B$9-A22)*1.5)</f>
+        <v/>
+      </c>
+      <c r="C22" s="39">
+        <f>B22-$B$8</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>C22*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E22" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C22*100,0)))&amp;REPT("▲",MAX(0,ROUND(C22*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>MEDICAL EXCEPTION IMPACT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>Exception %</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>Est. GTN %</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>Change</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D26" s="31" t="inlineStr">
         <is>
           <t>$ Impact</t>
         </is>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>Visual</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="43" t="n">
+    <row r="27">
+      <c r="A27" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="25">
+        <f>$B$8*(1-A27*0.5)</f>
+        <v/>
+      </c>
+      <c r="C27" s="39">
+        <f>B27-$B$8</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>C27*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E27" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C27*100,0)))&amp;REPT("▲",MAX(0,ROUND(C27*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B28" s="25">
+        <f>$B$8*(1-A28*0.5)</f>
+        <v/>
+      </c>
+      <c r="C28" s="39">
+        <f>B28-$B$8</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>C28*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E28" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C28*100,0)))&amp;REPT("▲",MAX(0,ROUND(C28*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="44" t="n">
         <v>0.1</v>
       </c>
-      <c r="B16" s="26">
-        <f>$B$8*(1+($B$9-A16)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C16" s="40">
-        <f>B16-$B$8</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>C16*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E16" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C16*100,0)))&amp;REPT("▲",MAX(0,ROUND(C16*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="n">
+      <c r="B29" s="25">
+        <f>$B$8*(1-A29*0.5)</f>
+        <v/>
+      </c>
+      <c r="C29" s="39">
+        <f>B29-$B$8</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>C29*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E29" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C29*100,0)))&amp;REPT("▲",MAX(0,ROUND(C29*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="44" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B30" s="25">
+        <f>$B$8*(1-A30*0.5)</f>
+        <v/>
+      </c>
+      <c r="C30" s="39">
+        <f>B30-$B$8</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>C30*Model!Q26</f>
+        <v/>
+      </c>
+      <c r="E30" s="45">
+        <f>REPT("▼",MAX(0,ROUND(-C30*100,0)))&amp;REPT("▲",MAX(0,ROUND(C30*100,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="n">
         <v>0.2</v>
       </c>
-      <c r="B17" s="26">
-        <f>$B$8*(1+($B$9-A17)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C17" s="40">
-        <f>B17-$B$8</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>C17*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E17" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C17*100,0)))&amp;REPT("▲",MAX(0,ROUND(C17*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B18" s="26">
-        <f>$B$8*(1+($B$9-A18)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C18" s="40">
-        <f>B18-$B$8</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>C18*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E18" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C18*100,0)))&amp;REPT("▲",MAX(0,ROUND(C18*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="B19" s="26">
-        <f>$B$8*(1+($B$9-A19)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C19" s="40">
-        <f>B19-$B$8</f>
-        <v/>
-      </c>
-      <c r="D19" s="25">
-        <f>C19*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E19" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C19*100,0)))&amp;REPT("▲",MAX(0,ROUND(C19*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B20" s="26">
-        <f>$B$8*(1+($B$9-A20)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C20" s="40">
-        <f>B20-$B$8</f>
-        <v/>
-      </c>
-      <c r="D20" s="25">
-        <f>C20*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E20" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C20*100,0)))&amp;REPT("▲",MAX(0,ROUND(C20*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="43" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="B21" s="26">
-        <f>$B$8*(1+($B$9-A21)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C21" s="40">
-        <f>B21-$B$8</f>
-        <v/>
-      </c>
-      <c r="D21" s="25">
-        <f>C21*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E21" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C21*100,0)))&amp;REPT("▲",MAX(0,ROUND(C21*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="43" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="B22" s="26">
-        <f>$B$8*(1+($B$9-A22)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C22" s="40">
-        <f>B22-$B$8</f>
-        <v/>
-      </c>
-      <c r="D22" s="25">
-        <f>C22*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E22" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C22*100,0)))&amp;REPT("▲",MAX(0,ROUND(C22*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="B23" s="26">
-        <f>$B$8*(1+($B$9-A23)*1.5)</f>
-        <v/>
-      </c>
-      <c r="C23" s="40">
-        <f>B23-$B$8</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>C23*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E23" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C23*100,0)))&amp;REPT("▲",MAX(0,ROUND(C23*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>MEDICAL EXCEPTION IMPACT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>Exception %</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>Est. GTN %</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>$ Impact</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B28" s="26">
-        <f>$B$8*(1-A28*0.5)</f>
-        <v/>
-      </c>
-      <c r="C28" s="40">
-        <f>B28-$B$8</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>C28*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E28" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C28*100,0)))&amp;REPT("▲",MAX(0,ROUND(C28*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="43" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B29" s="26">
-        <f>$B$8*(1-A29*0.5)</f>
-        <v/>
-      </c>
-      <c r="C29" s="40">
-        <f>B29-$B$8</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
-        <f>C29*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E29" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C29*100,0)))&amp;REPT("▲",MAX(0,ROUND(C29*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B30" s="26">
-        <f>$B$8*(1-A30*0.5)</f>
-        <v/>
-      </c>
-      <c r="C30" s="40">
-        <f>B30-$B$8</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
-        <f>C30*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E30" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C30*100,0)))&amp;REPT("▲",MAX(0,ROUND(C30*100,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="43" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B31" s="26">
+      <c r="B31" s="25">
         <f>$B$8*(1-A31*0.5)</f>
         <v/>
       </c>
-      <c r="C31" s="40">
+      <c r="C31" s="39">
         <f>B31-$B$8</f>
         <v/>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="24">
         <f>C31*Model!Q26</f>
         <v/>
       </c>
-      <c r="E31" s="44">
+      <c r="E31" s="45">
         <f>REPT("▼",MAX(0,ROUND(-C31*100,0)))&amp;REPT("▲",MAX(0,ROUND(C31*100,0)))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B32" s="26">
+      <c r="A32" s="44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B32" s="25">
         <f>$B$8*(1-A32*0.5)</f>
         <v/>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="39">
         <f>B32-$B$8</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="24">
         <f>C32*Model!Q26</f>
         <v/>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="45">
         <f>REPT("▼",MAX(0,ROUND(-C32*100,0)))&amp;REPT("▲",MAX(0,ROUND(C32*100,0)))</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="43" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="B33" s="26">
-        <f>$B$8*(1-A33*0.5)</f>
-        <v/>
-      </c>
-      <c r="C33" s="40">
-        <f>B33-$B$8</f>
-        <v/>
-      </c>
-      <c r="D33" s="25">
-        <f>C33*Model!Q26</f>
-        <v/>
-      </c>
-      <c r="E33" s="44">
-        <f>REPT("▼",MAX(0,ROUND(-C33*100,0)))&amp;REPT("▲",MAX(0,ROUND(C33*100,0)))</f>
-        <v/>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSIGHT</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Coverage has the HIGHEST impact on GTN. Each 10% increase in coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>reduces GTN by ~15% because fewer patients need the expensive Not Covered buydown.</t>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Coverage has the HIGHEST impact. +10% coverage ≈ -15% GTN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A38:E38"/>
+  <mergeCells count="6">
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A4:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>EXECUTIVE SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>ANNUAL GTN %</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PROGRAM COST</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>AVG COVERAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="45">
-        <f>Model!Q27</f>
-        <v/>
-      </c>
-      <c r="C7" s="46">
-        <f>Model!Q25</f>
-        <v/>
-      </c>
-      <c r="E7" s="47">
-        <f>AVERAGE(Model!E6:P6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8"/>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="A6:B6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Cardamyst Affordability Model.xlsx
+++ b/Cardamyst Affordability Model.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accruals" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
@@ -28,8 +29,9 @@
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%"/>
     <numFmt numFmtId="169" formatCode="+0.00%;-0.00%"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;+#,##0;[Red]&quot;$&quot;-#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,8 +140,19 @@
       <color rgb="0071B4BE"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D7AB5"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -188,6 +201,12 @@
         <bgColor rgb="00CCA1DD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF6600"/>
+        <bgColor rgb="00FF6600"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -229,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -284,6 +303,22 @@
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -362,7 +397,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -471,7 +505,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -641,7 +674,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -772,6 +804,135 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>GTN: Accrued (ExFactory) vs Actual (Rx)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Accruals'!B50</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="E31D93"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Accruals'!$A$51:$A$62</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Accruals'!$B$51:$B$62</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Accruals'!C50</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="71B4BE"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Accruals'!$A$51:$A$62</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Accruals'!$C$51:$C$62</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>GTN ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
@@ -936,6 +1097,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -966,6 +1130,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1062,6 +1229,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1073,9 +1243,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="4320000"/>
@@ -1127,6 +1297,61 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
@@ -1144,6 +1369,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4034,6 +4262,1594 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A4:Q76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GTN ACCRUALS - INCOME STATEMENT METHOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>For Finance: Accruals based on ExFactory revenue with GTN % from Rx demand model</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="O8" s="15" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
+        <is>
+          <t>ANNUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>EXFACTORY DEMAND (Sales to Wholesalers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ExFactory Units</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>474</v>
+      </c>
+      <c r="F11" s="47" t="n">
+        <v>130</v>
+      </c>
+      <c r="G11" s="47" t="n">
+        <v>376</v>
+      </c>
+      <c r="H11" s="47" t="n">
+        <v>644</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <v>1209</v>
+      </c>
+      <c r="J11" s="47" t="n">
+        <v>1973</v>
+      </c>
+      <c r="K11" s="47" t="n">
+        <v>3262</v>
+      </c>
+      <c r="L11" s="47" t="n">
+        <v>3786</v>
+      </c>
+      <c r="M11" s="47" t="n">
+        <v>4691</v>
+      </c>
+      <c r="N11" s="47" t="n">
+        <v>5235</v>
+      </c>
+      <c r="O11" s="47" t="n">
+        <v>6325</v>
+      </c>
+      <c r="P11" s="47" t="n">
+        <v>8673</v>
+      </c>
+      <c r="Q11" s="18">
+        <f>SUM(E11:P11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>WAC Price</t>
+        </is>
+      </c>
+      <c r="E12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="K12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="L12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="M12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="N12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="O12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+      <c r="P12" s="24">
+        <f>Assumptions!$C$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>ExFactory Gross Revenue</t>
+        </is>
+      </c>
+      <c r="E13" s="48">
+        <f>E11*E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="48">
+        <f>F11*F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="48">
+        <f>G11*G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="48">
+        <f>H11*H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="48">
+        <f>I11*I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="48">
+        <f>J11*J12</f>
+        <v/>
+      </c>
+      <c r="K13" s="48">
+        <f>K11*K12</f>
+        <v/>
+      </c>
+      <c r="L13" s="48">
+        <f>L11*L12</f>
+        <v/>
+      </c>
+      <c r="M13" s="48">
+        <f>M11*M12</f>
+        <v/>
+      </c>
+      <c r="N13" s="48">
+        <f>N11*N12</f>
+        <v/>
+      </c>
+      <c r="O13" s="48">
+        <f>O11*O12</f>
+        <v/>
+      </c>
+      <c r="P13" s="48">
+        <f>P11*P12</f>
+        <v/>
+      </c>
+      <c r="Q13" s="49">
+        <f>SUM(E13:P13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Script Demand (Rx)</t>
+        </is>
+      </c>
+      <c r="E15" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="50" t="n">
+        <v>130</v>
+      </c>
+      <c r="G15" s="50" t="n">
+        <v>246</v>
+      </c>
+      <c r="H15" s="50" t="n">
+        <v>445</v>
+      </c>
+      <c r="I15" s="50" t="n">
+        <v>827</v>
+      </c>
+      <c r="J15" s="50" t="n">
+        <v>1273</v>
+      </c>
+      <c r="K15" s="50" t="n">
+        <v>2290</v>
+      </c>
+      <c r="L15" s="50" t="n">
+        <v>3028</v>
+      </c>
+      <c r="M15" s="50" t="n">
+        <v>3919</v>
+      </c>
+      <c r="N15" s="50" t="n">
+        <v>4772</v>
+      </c>
+      <c r="O15" s="50" t="n">
+        <v>5745</v>
+      </c>
+      <c r="P15" s="50" t="n">
+        <v>6813</v>
+      </c>
+      <c r="Q15" s="18">
+        <f>SUM(E15:P15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MOH Target</t>
+        </is>
+      </c>
+      <c r="E16" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L16" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N16" s="51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" s="51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P16" s="51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Channel Inventory (EOM)</t>
+        </is>
+      </c>
+      <c r="E17" s="18">
+        <f>E15*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="18">
+        <f>F15*F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="18">
+        <f>G15*G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="18">
+        <f>H15*H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="18">
+        <f>I15*I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="18">
+        <f>J15*J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
+        <f>K15*K16</f>
+        <v/>
+      </c>
+      <c r="L17" s="18">
+        <f>L15*L16</f>
+        <v/>
+      </c>
+      <c r="M17" s="18">
+        <f>M15*M16</f>
+        <v/>
+      </c>
+      <c r="N17" s="18">
+        <f>N15*N16</f>
+        <v/>
+      </c>
+      <c r="O17" s="18">
+        <f>O15*O16</f>
+        <v/>
+      </c>
+      <c r="P17" s="18">
+        <f>P15*P16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ExFactory vs Rx Demand Ratio</t>
+        </is>
+      </c>
+      <c r="E18" s="52">
+        <f>IFERROR(E11/E15,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="52">
+        <f>IFERROR(F11/F15,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="52">
+        <f>IFERROR(G11/G15,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="52">
+        <f>IFERROR(H11/H15,0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="52">
+        <f>IFERROR(I11/I15,0)</f>
+        <v/>
+      </c>
+      <c r="J18" s="52">
+        <f>IFERROR(J11/J15,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="52">
+        <f>IFERROR(K11/K15,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="52">
+        <f>IFERROR(L11/L15,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="52">
+        <f>IFERROR(M11/M15,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="52">
+        <f>IFERROR(N11/N15,0)</f>
+        <v/>
+      </c>
+      <c r="O18" s="52">
+        <f>IFERROR(O11/O15,0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="52">
+        <f>IFERROR(P11/P15,0)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="52">
+        <f>IFERROR(Q11/Q15,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>GTN ACCRUAL (Income Statement Method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Rx Demand GTN % (from Model)</t>
+        </is>
+      </c>
+      <c r="E21" s="25">
+        <f>Model!E27</f>
+        <v/>
+      </c>
+      <c r="F21" s="25">
+        <f>Model!F27</f>
+        <v/>
+      </c>
+      <c r="G21" s="25">
+        <f>Model!G27</f>
+        <v/>
+      </c>
+      <c r="H21" s="25">
+        <f>Model!H27</f>
+        <v/>
+      </c>
+      <c r="I21" s="25">
+        <f>Model!I27</f>
+        <v/>
+      </c>
+      <c r="J21" s="25">
+        <f>Model!J27</f>
+        <v/>
+      </c>
+      <c r="K21" s="25">
+        <f>Model!K27</f>
+        <v/>
+      </c>
+      <c r="L21" s="25">
+        <f>Model!L27</f>
+        <v/>
+      </c>
+      <c r="M21" s="25">
+        <f>Model!M27</f>
+        <v/>
+      </c>
+      <c r="N21" s="25">
+        <f>Model!N27</f>
+        <v/>
+      </c>
+      <c r="O21" s="25">
+        <f>Model!O27</f>
+        <v/>
+      </c>
+      <c r="P21" s="25">
+        <f>Model!P27</f>
+        <v/>
+      </c>
+      <c r="Q21" s="25">
+        <f>Model!Q27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" s="53" t="inlineStr">
+        <is>
+          <t>GTN Accrual (ExFactory × GTN%)</t>
+        </is>
+      </c>
+      <c r="E22" s="54">
+        <f>E13*E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="54">
+        <f>F13*F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="54">
+        <f>G13*G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="54">
+        <f>H13*H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="54">
+        <f>I13*I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="54">
+        <f>J13*J21</f>
+        <v/>
+      </c>
+      <c r="K22" s="54">
+        <f>K13*K21</f>
+        <v/>
+      </c>
+      <c r="L22" s="54">
+        <f>L13*L21</f>
+        <v/>
+      </c>
+      <c r="M22" s="54">
+        <f>M13*M21</f>
+        <v/>
+      </c>
+      <c r="N22" s="54">
+        <f>N13*N21</f>
+        <v/>
+      </c>
+      <c r="O22" s="54">
+        <f>O13*O21</f>
+        <v/>
+      </c>
+      <c r="P22" s="54">
+        <f>P13*P21</f>
+        <v/>
+      </c>
+      <c r="Q22" s="55">
+        <f>SUM(E22:P22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Net Revenue (ExFactory - Accrual)</t>
+        </is>
+      </c>
+      <c r="E23" s="24">
+        <f>E13-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>F13-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="24">
+        <f>G13-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="24">
+        <f>H13-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="24">
+        <f>I13-I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="24">
+        <f>J13-J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="24">
+        <f>K13-K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="24">
+        <f>L13-L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="24">
+        <f>M13-M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="24">
+        <f>N13-N22</f>
+        <v/>
+      </c>
+      <c r="O23" s="24">
+        <f>O13-O22</f>
+        <v/>
+      </c>
+      <c r="P23" s="24">
+        <f>P13-P22</f>
+        <v/>
+      </c>
+      <c r="Q23" s="56">
+        <f>SUM(E23:P23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>ACCRUAL vs ACTUAL COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Actual GTN Costs (Rx-based)</t>
+        </is>
+      </c>
+      <c r="E27" s="36">
+        <f>Model!E25</f>
+        <v/>
+      </c>
+      <c r="F27" s="36">
+        <f>Model!F25</f>
+        <v/>
+      </c>
+      <c r="G27" s="36">
+        <f>Model!G25</f>
+        <v/>
+      </c>
+      <c r="H27" s="36">
+        <f>Model!H25</f>
+        <v/>
+      </c>
+      <c r="I27" s="36">
+        <f>Model!I25</f>
+        <v/>
+      </c>
+      <c r="J27" s="36">
+        <f>Model!J25</f>
+        <v/>
+      </c>
+      <c r="K27" s="36">
+        <f>Model!K25</f>
+        <v/>
+      </c>
+      <c r="L27" s="36">
+        <f>Model!L25</f>
+        <v/>
+      </c>
+      <c r="M27" s="36">
+        <f>Model!M25</f>
+        <v/>
+      </c>
+      <c r="N27" s="36">
+        <f>Model!N25</f>
+        <v/>
+      </c>
+      <c r="O27" s="36">
+        <f>Model!O25</f>
+        <v/>
+      </c>
+      <c r="P27" s="36">
+        <f>Model!P25</f>
+        <v/>
+      </c>
+      <c r="Q27" s="24">
+        <f>SUM(E27:P27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Accrued GTN (ExFactory-based)</t>
+        </is>
+      </c>
+      <c r="E28" s="36">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F28" s="36">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="G28" s="36">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="H28" s="36">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="I28" s="36">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="J28" s="36">
+        <f>J22</f>
+        <v/>
+      </c>
+      <c r="K28" s="36">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="L28" s="36">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="M28" s="36">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="N28" s="36">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="O28" s="36">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="P28" s="36">
+        <f>P22</f>
+        <v/>
+      </c>
+      <c r="Q28" s="24">
+        <f>SUM(E28:P28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Variance (Accrued - Actual)</t>
+        </is>
+      </c>
+      <c r="E29" s="40">
+        <f>E28-E27</f>
+        <v/>
+      </c>
+      <c r="F29" s="40">
+        <f>F28-F27</f>
+        <v/>
+      </c>
+      <c r="G29" s="40">
+        <f>G28-G27</f>
+        <v/>
+      </c>
+      <c r="H29" s="40">
+        <f>H28-H27</f>
+        <v/>
+      </c>
+      <c r="I29" s="40">
+        <f>I28-I27</f>
+        <v/>
+      </c>
+      <c r="J29" s="40">
+        <f>J28-J27</f>
+        <v/>
+      </c>
+      <c r="K29" s="40">
+        <f>K28-K27</f>
+        <v/>
+      </c>
+      <c r="L29" s="40">
+        <f>L28-L27</f>
+        <v/>
+      </c>
+      <c r="M29" s="40">
+        <f>M28-M27</f>
+        <v/>
+      </c>
+      <c r="N29" s="40">
+        <f>N28-N27</f>
+        <v/>
+      </c>
+      <c r="O29" s="40">
+        <f>O28-O27</f>
+        <v/>
+      </c>
+      <c r="P29" s="40">
+        <f>P28-P27</f>
+        <v/>
+      </c>
+      <c r="Q29" s="57">
+        <f>SUM(E29:P29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="E30" s="38">
+        <f>IFERROR(E29/E27,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="38">
+        <f>IFERROR(F29/F27,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="38">
+        <f>IFERROR(G29/G27,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="38">
+        <f>IFERROR(H29/H27,0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="38">
+        <f>IFERROR(I29/I27,0)</f>
+        <v/>
+      </c>
+      <c r="J30" s="38">
+        <f>IFERROR(J29/J27,0)</f>
+        <v/>
+      </c>
+      <c r="K30" s="38">
+        <f>IFERROR(K29/K27,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="38">
+        <f>IFERROR(L29/L27,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="38">
+        <f>IFERROR(M29/M27,0)</f>
+        <v/>
+      </c>
+      <c r="N30" s="38">
+        <f>IFERROR(N29/N27,0)</f>
+        <v/>
+      </c>
+      <c r="O30" s="38">
+        <f>IFERROR(O29/O27,0)</f>
+        <v/>
+      </c>
+      <c r="P30" s="38">
+        <f>IFERROR(P29/P27,0)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="38">
+        <f>IFERROR(Q29/Q27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Cumulative Variance</t>
+        </is>
+      </c>
+      <c r="E31" s="24">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="40">
+        <f>E31+F29</f>
+        <v/>
+      </c>
+      <c r="G31" s="40">
+        <f>F31+G29</f>
+        <v/>
+      </c>
+      <c r="H31" s="40">
+        <f>G31+H29</f>
+        <v/>
+      </c>
+      <c r="I31" s="40">
+        <f>H31+I29</f>
+        <v/>
+      </c>
+      <c r="J31" s="40">
+        <f>I31+J29</f>
+        <v/>
+      </c>
+      <c r="K31" s="40">
+        <f>J31+K29</f>
+        <v/>
+      </c>
+      <c r="L31" s="40">
+        <f>K31+L29</f>
+        <v/>
+      </c>
+      <c r="M31" s="40">
+        <f>L31+M29</f>
+        <v/>
+      </c>
+      <c r="N31" s="40">
+        <f>M31+N29</f>
+        <v/>
+      </c>
+      <c r="O31" s="40">
+        <f>N31+O29</f>
+        <v/>
+      </c>
+      <c r="P31" s="40">
+        <f>O31+P29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>ACCRUAL RESERVE BALANCE (Balance Sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="E35" s="58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="24">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="G35" s="24">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="H35" s="24">
+        <f>G38</f>
+        <v/>
+      </c>
+      <c r="I35" s="24">
+        <f>H38</f>
+        <v/>
+      </c>
+      <c r="J35" s="24">
+        <f>I38</f>
+        <v/>
+      </c>
+      <c r="K35" s="24">
+        <f>J38</f>
+        <v/>
+      </c>
+      <c r="L35" s="24">
+        <f>K38</f>
+        <v/>
+      </c>
+      <c r="M35" s="24">
+        <f>L38</f>
+        <v/>
+      </c>
+      <c r="N35" s="24">
+        <f>M38</f>
+        <v/>
+      </c>
+      <c r="O35" s="24">
+        <f>N38</f>
+        <v/>
+      </c>
+      <c r="P35" s="24">
+        <f>O38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>+ Accrual (I/S Charge)</t>
+        </is>
+      </c>
+      <c r="E36" s="24">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="F36" s="24">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="G36" s="24">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="H36" s="24">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="I36" s="24">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="J36" s="24">
+        <f>J22</f>
+        <v/>
+      </c>
+      <c r="K36" s="24">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="L36" s="24">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="M36" s="24">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="N36" s="24">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="O36" s="24">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="P36" s="24">
+        <f>P22</f>
+        <v/>
+      </c>
+      <c r="Q36" s="24">
+        <f>SUM(E36:P36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>- Actual Payments</t>
+        </is>
+      </c>
+      <c r="E37" s="24">
+        <f>E27</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>F27</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>G27</f>
+        <v/>
+      </c>
+      <c r="H37" s="24">
+        <f>H27</f>
+        <v/>
+      </c>
+      <c r="I37" s="24">
+        <f>I27</f>
+        <v/>
+      </c>
+      <c r="J37" s="24">
+        <f>J27</f>
+        <v/>
+      </c>
+      <c r="K37" s="24">
+        <f>K27</f>
+        <v/>
+      </c>
+      <c r="L37" s="24">
+        <f>L27</f>
+        <v/>
+      </c>
+      <c r="M37" s="24">
+        <f>M27</f>
+        <v/>
+      </c>
+      <c r="N37" s="24">
+        <f>N27</f>
+        <v/>
+      </c>
+      <c r="O37" s="24">
+        <f>O27</f>
+        <v/>
+      </c>
+      <c r="P37" s="24">
+        <f>P27</f>
+        <v/>
+      </c>
+      <c r="Q37" s="24">
+        <f>SUM(E37:P37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E38" s="28">
+        <f>E35+E36-E37</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>F35+F36-F37</f>
+        <v/>
+      </c>
+      <c r="G38" s="28">
+        <f>G35+G36-G37</f>
+        <v/>
+      </c>
+      <c r="H38" s="28">
+        <f>H35+H36-H37</f>
+        <v/>
+      </c>
+      <c r="I38" s="28">
+        <f>I35+I36-I37</f>
+        <v/>
+      </c>
+      <c r="J38" s="28">
+        <f>J35+J36-J37</f>
+        <v/>
+      </c>
+      <c r="K38" s="28">
+        <f>K35+K36-K37</f>
+        <v/>
+      </c>
+      <c r="L38" s="28">
+        <f>L35+L36-L37</f>
+        <v/>
+      </c>
+      <c r="M38" s="28">
+        <f>M35+M36-M37</f>
+        <v/>
+      </c>
+      <c r="N38" s="28">
+        <f>N35+N36-N37</f>
+        <v/>
+      </c>
+      <c r="O38" s="28">
+        <f>O35+O36-O37</f>
+        <v/>
+      </c>
+      <c r="P38" s="28">
+        <f>P35+P36-P37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>KEY METRICS FOR FINANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Annual ExFactory Revenue</t>
+        </is>
+      </c>
+      <c r="C42" s="59">
+        <f>Q13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Annual GTN Accrual</t>
+        </is>
+      </c>
+      <c r="C43" s="59">
+        <f>Q22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Annual Net Revenue</t>
+        </is>
+      </c>
+      <c r="C44" s="59">
+        <f>Q23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Effective GTN Rate</t>
+        </is>
+      </c>
+      <c r="C45" s="60">
+        <f>Q22/Q13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Accrual vs Actual Variance</t>
+        </is>
+      </c>
+      <c r="C46" s="61">
+        <f>Q29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Year-End Reserve Balance</t>
+        </is>
+      </c>
+      <c r="C47" s="59">
+        <f>P38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B50" s="42" t="inlineStr">
+        <is>
+          <t>Accrued</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B51" s="24">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="C51" s="24">
+        <f>E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B52" s="24">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="C52" s="24">
+        <f>F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B53" s="24">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="C53" s="24">
+        <f>G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B54" s="24">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="C54" s="24">
+        <f>H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B55" s="24">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="C55" s="24">
+        <f>I27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B56" s="24">
+        <f>J28</f>
+        <v/>
+      </c>
+      <c r="C56" s="24">
+        <f>J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B57" s="24">
+        <f>K28</f>
+        <v/>
+      </c>
+      <c r="C57" s="24">
+        <f>K27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B58" s="24">
+        <f>L28</f>
+        <v/>
+      </c>
+      <c r="C58" s="24">
+        <f>L27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B59" s="24">
+        <f>M28</f>
+        <v/>
+      </c>
+      <c r="C59" s="24">
+        <f>M27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B60" s="24">
+        <f>N28</f>
+        <v/>
+      </c>
+      <c r="C60" s="24">
+        <f>N27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B61" s="24">
+        <f>O28</f>
+        <v/>
+      </c>
+      <c r="C61" s="24">
+        <f>O27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B62" s="24">
+        <f>P28</f>
+        <v/>
+      </c>
+      <c r="C62" s="24">
+        <f>P27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO USE FOR ACCRUALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>1. ExFactory Units (row 11): Update monthly with actual shipments to wholesalers</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>2. GTN Accrual (row 22): Book this to I/S as contra-revenue each month</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>3. Actual GTN Costs (row 27): From Rx demand model - reconcile as claims come in</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>4. Variance (row 29): Positive = over-accrued (favorable), Negative = under-accrued</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>5. Reserve Balance (row 38): Should be positive; tracks timing difference</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>WHY VARIANCE EXISTS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>• ExFactory ≠ Rx Demand due to channel inventory buildup/drawdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>• GTN % applies to Rx at point of dispensing, not ExFactory shipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>• Early months: ExFactory &gt; Rx (building inventory) → Over-accrual</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>• Later months: May reverse as inventory normalizes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D7:P7"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A71:G71"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A4:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5051,7 +6867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
